--- a/PSCBOX_YANGPYEONG_DIAPHRAGM_BB.xlsx
+++ b/PSCBOX_YANGPYEONG_DIAPHRAGM_BB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#   덕트 · 매입물 : 이 도면에는 없다</t>
+          <t>#   덕트 : 2-072 에는 없다 — 2-136 강연선 배치 단면도(19) 의 주두부단면 치수로 넣었다 (아래 DUCT 블록)</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,6 @@
       <c r="B14" t="n">
         <v>500</v>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>격벽 두께(교축) — 도면에 치수 없음. 폐합철근 짧은 변 380 + 2 × 60 으로 어림 (가정 · 3D 고리에만 쓰인다)</t>
@@ -1130,552 +1129,3065 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t># ================= REBAR — 격벽 철근만 (상부슬래브 1-1 · 1-2 · 1-3 · 2 · 3 · 복부 7-2 · 7-3 · 8-2 · 8-3 · 하부 9-2 · 9-3 은 아직) =================</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>#   D 철근은 **폐합철근**이다 — 도면 상세 : 짧은 변 380 · 겹이음 L1 · L2 · J. 단면에서는 선 하나로 보인다.</t>
+          <t># ================= DUCT (2-136 강연선 배치 단면도(19) · 90M 구간 · SEG.M18 — 「주두부단면」 치수) =================</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>#   덕트가 없으므로 미는 장은 없다. 개구부(자르는 장)가 세로 · 가로 고리를 자른다.</t>
+          <t># duct | id | shape | D | H | x | y | ref | clr        (문법은 bim_duct.js)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   2-136 은 축척이 하나가 아니다 (폭 12,000 과 깊이가 종이에서 다른 배율) — 자리는 **치수 글자**에서 읽었다. 반단면 · 좌우 대칭.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t># crebar | id | dia | plane | at | set | lap | from | to | ctc</t>
+          <t>#     상단 (깊이 160) : 2,700 · 3@150 · 300 · 3@150 · 300 · 3@150 · 350 · 1,150 · 300 · 3@150 · 300 · 3@150 · 300 · 3@150 · 3,600 = 12,000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>#   D10 세로 고리 (H19) : 도면 77 줄 x = 125k (k −38 … 38, 「76@125 = 9,500」) — 도면은 길이로 D10 · D11 · D12 로 갈린다. 여기서는 한 행</t>
+          <t>#       → x 2,700 ~ 3,150 · 3,450 ~ 3,900 · 4,200 ~ 4,650 · 6,450 ~ 6,900 · 7,200 ~ 7,650 · 7,950 ~ 8,400  (넷씩 · 150)  — TS2 · TC3 ~ TC35</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>19</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>yz</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-4750~4750</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>125</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>vertical hoops D10/D11/D12 — 77 stations at 125, cut by the opening</t>
+          <t>#     하단 (깊이 370 = 160 + 210) : 3,900 · 300 · 3@150 · 1,800 · 3@150 · 300 · 4,800 (「주두부, A18」) + TC1 x 5,000 · TC2 x 6,150 (상단 줄의 350 · 1,150 눈금)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>#   D1 가로 고리 (H22) : 도면 66 줄 y −814 … −8,941 (125 간격 · 도면 y) → 모형 y −834 … −8,961.</t>
+          <t>#   지름 110 : 그림의 원 8.6 pt × 12.87 mm/pt (150 간격으로 잰 배율) — 도면에 외경 표기는 없다</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>#     상부슬래브 안(−780 위)에는 없다. 도면은 표에서 D1 ~ D8 로 갈린다 (D6 ~ D8 은 H19 · 왼쪽 복부 쪽 — 자리 미확인). 여기서는 한 행 · H22</t>
+          <t>#   깊이 : 그림에서 다시 재면 위 160 · 아래 371 (데크 면에서 · ref deck). 데크 면은 크라운 ±1,000 밖에서 도면과 같다</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>22</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-8961~-834</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
-        <v>125</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>horizontal hoops D1..D8 — 66 levels at 125, cut by the opening</t>
+          <t>#   ! 그림의 원 몇 개(TS2 · TC3 · TC4)는 치수와 36 ~ 150 어긋나게 그려졌다 — 치수를 따랐다</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   clr 0 — 북실 P1 과 같은 결정(「가」 · 도면 수준). 도면 2-072 의 격벽 철근은 덕트를 피하지 않고 그려져 있다 (도면끼리 따로 그림)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t># srebar code 1 : 개구부 보강 — 길이 고정(8 번 칸 len · 도면 표) · 개구부 면으로 끌려가 J 최소에 앉는다(9 번 칸 seat open)</t>
+          <t># --- left : 상단 (깊이 160) ---</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | len | seat | | | z</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UL1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>110</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-2700</v>
+      </c>
+      <c r="G67" t="n">
+        <v>160</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>#   init 은 출발점 — 도면 녹색 선에서 잰 가운데(넷 중 2 · 3 번 사이)의 중점, y 는 도면 − 20. 넷씩 · 간격 50 (도면 49.5 ~ 50)</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UL2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>110</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-2850</v>
+      </c>
+      <c r="G68" t="n">
+        <v>160</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>#   D13 H16 L 1,465 : 세로 4 + 4 · 가로 위 4 · 아래 4      ! 도면 그림의 가로는 위 1,435 · 아래 1,711 (표와 다르다)</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UL3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>110</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>160</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>#   D14 H16 L 1,420 : 위 모서리 접기(500) 사선 4 + 4</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>UL4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>110</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-3150</v>
+      </c>
+      <c r="G70" t="n">
+        <v>160</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>#   D15 H16 L 1,070 : 아래 모서리 접기(250) 사선 4 + 4</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UL5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>110</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-3450</v>
+      </c>
+      <c r="G71" t="n">
+        <v>160</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>D13-L</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
+          <t>UL6</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D72" t="n">
-        <v>16</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-863.5,-6945,90</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-3600</v>
+      </c>
       <c r="G72" t="n">
-        <v>4</v>
-      </c>
-      <c r="H72" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I72" t="n">
-        <v>1465</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>opening bar D13, vertical, left</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D13-R</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
+          <t>UL7</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>863.5,-6945,90</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-3750</v>
+      </c>
       <c r="G73" t="n">
-        <v>4</v>
-      </c>
-      <c r="H73" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I73" t="n">
-        <v>1465</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>opening bar D13, vertical, right</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D13-T</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
+          <t>UL8</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0,-5954,0</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-3900</v>
+      </c>
       <c r="G74" t="n">
-        <v>4</v>
-      </c>
-      <c r="H74" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I74" t="n">
-        <v>1465</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>opening bar D13, horizontal, above</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D13-B</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
+          <t>UL9</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D75" t="n">
-        <v>16</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0,-7685.5,0</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-4200</v>
+      </c>
       <c r="G75" t="n">
-        <v>4</v>
-      </c>
-      <c r="H75" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I75" t="n">
-        <v>1465</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>opening bar D13, horizontal, below</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D14-UL</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
+          <t>UL10</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D76" t="n">
-        <v>16</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-580.5,-6238,45</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-4350</v>
+      </c>
       <c r="G76" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I76" t="n">
-        <v>1420</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>opening bar D14, diagonal, upper-left chamfer</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>D14-UR</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
+          <t>UL11</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D77" t="n">
-        <v>16</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>583,-6238,135</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-4500</v>
+      </c>
       <c r="G77" t="n">
-        <v>4</v>
-      </c>
-      <c r="H77" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I77" t="n">
-        <v>1420</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>opening bar D14, diagonal, upper-right chamfer</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D15-LL</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
+          <t>UL12</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-706.8,-7526.8,135</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-4650</v>
+      </c>
       <c r="G78" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I78" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>opening bar D15, diagonal, lower-left chamfer</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>srebar</t>
+          <t>duct</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D15-LR</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
+          <t>UL13</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
       </c>
       <c r="D79" t="n">
-        <v>16</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>707.4,-7526.6,45</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-6450</v>
+      </c>
       <c r="G79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H79" t="n">
-        <v>50</v>
+        <v>160</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
       </c>
       <c r="I79" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>opening bar D15, diagonal, lower-right chamfer</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UL14</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>110</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-6600</v>
+      </c>
+      <c r="G80" t="n">
+        <v>160</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UL15</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>110</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-6750</v>
+      </c>
+      <c r="G81" t="n">
+        <v>160</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>UL16</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>110</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="G82" t="n">
+        <v>160</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UL17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>110</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-7200</v>
+      </c>
+      <c r="G83" t="n">
+        <v>160</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UL18</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>110</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-7350</v>
+      </c>
+      <c r="G84" t="n">
+        <v>160</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UL19</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>110</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="G85" t="n">
+        <v>160</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UL20</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>110</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-7650</v>
+      </c>
+      <c r="G86" t="n">
+        <v>160</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>UL21</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>110</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-7950</v>
+      </c>
+      <c r="G87" t="n">
+        <v>160</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UL22</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>110</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-8100</v>
+      </c>
+      <c r="G88" t="n">
+        <v>160</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UL23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>110</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-8250</v>
+      </c>
+      <c r="G89" t="n">
+        <v>160</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>UL24</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>110</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-8400</v>
+      </c>
+      <c r="G90" t="n">
+        <v>160</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t># --- left : 하단 (깊이 370) · TC1 5,000 · TC2 6,150 포함 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DL1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>110</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-3900</v>
+      </c>
+      <c r="G92" t="n">
+        <v>370</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DL2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>110</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="G93" t="n">
+        <v>370</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DL3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>110</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-4350</v>
+      </c>
+      <c r="G94" t="n">
+        <v>370</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>DL4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>110</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G95" t="n">
+        <v>370</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DL5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>110</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-4650</v>
+      </c>
+      <c r="G96" t="n">
+        <v>370</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DL6</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>110</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G97" t="n">
+        <v>370</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DL7</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>110</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-6150</v>
+      </c>
+      <c r="G98" t="n">
+        <v>370</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DL8</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>110</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-6450</v>
+      </c>
+      <c r="G99" t="n">
+        <v>370</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DL9</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>110</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-6600</v>
+      </c>
+      <c r="G100" t="n">
+        <v>370</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DL10</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>110</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-6750</v>
+      </c>
+      <c r="G101" t="n">
+        <v>370</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DL11</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>110</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="G102" t="n">
+        <v>370</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DL12</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>110</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-7200</v>
+      </c>
+      <c r="G103" t="n">
+        <v>370</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t># --- right : 상단 (깊이 160) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UR1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>110</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G105" t="n">
+        <v>160</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UR2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>110</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G106" t="n">
+        <v>160</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>UR3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>110</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G107" t="n">
+        <v>160</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>UR4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>110</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G108" t="n">
+        <v>160</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UR5</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>110</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G109" t="n">
+        <v>160</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UR6</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>110</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G110" t="n">
+        <v>160</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>UR7</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>110</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G111" t="n">
+        <v>160</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UR8</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>110</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G112" t="n">
+        <v>160</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>UR9</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>110</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G113" t="n">
+        <v>160</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UR10</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>110</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4350</v>
+      </c>
+      <c r="G114" t="n">
+        <v>160</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>UR11</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>110</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G115" t="n">
+        <v>160</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UR12</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>110</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G116" t="n">
+        <v>160</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UR13</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>110</v>
+      </c>
+      <c r="F117" t="n">
+        <v>6450</v>
+      </c>
+      <c r="G117" t="n">
+        <v>160</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UR14</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>110</v>
+      </c>
+      <c r="F118" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G118" t="n">
+        <v>160</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UR15</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>110</v>
+      </c>
+      <c r="F119" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G119" t="n">
+        <v>160</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UR16</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>110</v>
+      </c>
+      <c r="F120" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G120" t="n">
+        <v>160</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UR17</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>110</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G121" t="n">
+        <v>160</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UR18</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>110</v>
+      </c>
+      <c r="F122" t="n">
+        <v>7350</v>
+      </c>
+      <c r="G122" t="n">
+        <v>160</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UR19</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>110</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G123" t="n">
+        <v>160</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UR20</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>110</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7650</v>
+      </c>
+      <c r="G124" t="n">
+        <v>160</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UR21</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>110</v>
+      </c>
+      <c r="F125" t="n">
+        <v>7950</v>
+      </c>
+      <c r="G125" t="n">
+        <v>160</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UR22</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>110</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G126" t="n">
+        <v>160</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>110</v>
+      </c>
+      <c r="F127" t="n">
+        <v>8250</v>
+      </c>
+      <c r="G127" t="n">
+        <v>160</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UR24</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>110</v>
+      </c>
+      <c r="F128" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G128" t="n">
+        <v>160</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t># --- right : 하단 (깊이 370) · TC1 5,000 · TC2 6,150 포함 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DR1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>110</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G130" t="n">
+        <v>370</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DR2</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>110</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G131" t="n">
+        <v>370</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DR3</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>110</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4350</v>
+      </c>
+      <c r="G132" t="n">
+        <v>370</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DR4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>110</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G133" t="n">
+        <v>370</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DR5</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>110</v>
+      </c>
+      <c r="F134" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G134" t="n">
+        <v>370</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DR6</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>110</v>
+      </c>
+      <c r="F135" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G135" t="n">
+        <v>370</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DR7</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>110</v>
+      </c>
+      <c r="F136" t="n">
+        <v>6150</v>
+      </c>
+      <c r="G136" t="n">
+        <v>370</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DR8</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>110</v>
+      </c>
+      <c r="F137" t="n">
+        <v>6450</v>
+      </c>
+      <c r="G137" t="n">
+        <v>370</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DR9</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>110</v>
+      </c>
+      <c r="F138" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G138" t="n">
+        <v>370</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DR10</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>110</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6750</v>
+      </c>
+      <c r="G139" t="n">
+        <v>370</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>DR11</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>110</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G140" t="n">
+        <v>370</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DR12</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>110</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G141" t="n">
+        <v>370</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t># ================= REBAR — 격벽 철근만 (상부슬래브 1-1 · 1-2 · 1-3 · 2 · 3 · 복부 7-2 · 7-3 · 8-2 · 8-3 · 하부 9-2 · 9-3 은 아직) =================</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>#   D 철근은 **폐합철근**이다 — 도면 상세 : 짧은 변 380 · 겹이음 L1 · L2 · J. 단면에서는 선 하나로 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>#   덕트가 없으므로 미는 장은 없다. 개구부(자르는 장)가 세로 · 가로 고리를 자른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t># crebar | id | dia | plane | at | set | lap | from | to | ctc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>#   D10 세로 고리 (H19) : 도면 77 줄 x = 125k (k −38 … 38, 「76@125 = 9,500」) — 도면은 길이로 D10 · D11 · D12 로 갈린다. 여기서는 한 행</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>19</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>yz</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-4750~4750</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>125</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>vertical hoops D10/D11/D12 — 77 stations at 125, cut by the opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>#   D1 가로 고리 (H22) : 도면 66 줄 y −814 … −8,941 (125 간격 · 도면 y) → 모형 y −834 … −8,961.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>#     상부슬래브 안(−780 위)에는 없다. 도면은 표에서 D1 ~ D8 로 갈린다 (D6 ~ D8 은 H19 · 왼쪽 복부 쪽 — 자리 미확인). 여기서는 한 행 · H22</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>22</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-8961~-834</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>125</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>horizontal hoops D1..D8 — 66 levels at 125, cut by the opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t># srebar code 1 : 개구부 보강 — 길이 고정(8 번 칸 len · 도면 표) · 개구부 면으로 끌려가 J 최소에 앉는다(9 번 칸 seat open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | len | seat | | | z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>#   init 은 출발점 — 도면 녹색 선에서 잰 가운데(넷 중 2 · 3 번 사이)의 중점, y 는 도면 − 20. 넷씩 · 간격 50 (도면 49.5 ~ 50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>#   D13 H16 L 1,465 : 세로 4 + 4 · 가로 위 4 · 아래 4      ! 도면 그림의 가로는 위 1,435 · 아래 1,711 (표와 다르다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>#   D14 H16 L 1,420 : 위 모서리 접기(500) 사선 4 + 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>#   D15 H16 L 1,070 : 아래 모서리 접기(250) 사선 4 + 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D13-L</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>16</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-863.5,-6945,90</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>4</v>
+      </c>
+      <c r="H159" t="n">
+        <v>50</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1465</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>opening bar D13, vertical, left</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D13-R</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>16</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>863.5,-6945,90</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>4</v>
+      </c>
+      <c r="H160" t="n">
+        <v>50</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1465</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>opening bar D13, vertical, right</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D13-T</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>16</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0,-5954,0</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>50</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1465</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>opening bar D13, horizontal, above</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D13-B</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>16</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0,-7685.5,0</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="n">
+        <v>50</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1465</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>opening bar D13, horizontal, below</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D14-UL</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>16</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-580.5,-6238,45</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>4</v>
+      </c>
+      <c r="H163" t="n">
+        <v>50</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1420</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>opening bar D14, diagonal, upper-left chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D14-UR</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>16</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>583,-6238,135</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>4</v>
+      </c>
+      <c r="H164" t="n">
+        <v>50</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1420</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>opening bar D14, diagonal, upper-right chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D15-LL</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>16</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-706.8,-7526.8,135</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>4</v>
+      </c>
+      <c r="H165" t="n">
+        <v>50</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>opening bar D15, diagonal, lower-left chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D15-LR</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>16</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>707.4,-7526.6,45</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>4</v>
+      </c>
+      <c r="H166" t="n">
+        <v>50</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>opening bar D15, diagonal, lower-right chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>end</t>
         </is>
